--- a/artfynd/A 6062-2025 artfynd.xlsx
+++ b/artfynd/A 6062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>97382015</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552379.5496900012</v>
+        <v>552379</v>
       </c>
       <c r="R2" t="n">
-        <v>6313322.045660002</v>
+        <v>6313321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,43 +788,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97382016</v>
+        <v>97382014</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552379.5496900012</v>
+        <v>552340</v>
       </c>
       <c r="R3" t="n">
-        <v>6313322.045660002</v>
+        <v>6313281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +867,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,6 +894,225 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97382028</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar mellan Barkebo och Uvahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552412</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6313117</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97382016</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar mellan Barkebo och Uvahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552379</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6313321</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>

--- a/artfynd/A 6062-2025 artfynd.xlsx
+++ b/artfynd/A 6062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97382015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97382014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97382028</t>
         </is>
       </c>
     </row>
@@ -1117,8 +1137,19 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97382016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>